--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104466_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104466_W1.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4442</v>
+        <v>7.6155</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5224</v>
+        <v>6.353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9218</v>
+        <v>1.2625</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9542</v>
+        <v>2.9558</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.335</v>
+        <v>-0.3224</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2892</v>
+        <v>3.2782</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0709</v>
+        <v>2.0512</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7187</v>
+        <v>2.703</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8833</v>
+        <v>0.9046</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1705</v>
+        <v>1.3426</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1735</v>
+        <v>1.0334</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.003</v>
+        <v>0.3093</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5102</v>
+        <v>5.8163</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5574</v>
+        <v>3.7202</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9528</v>
+        <v>2.0961</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0791</v>
+        <v>5.081</v>
       </c>
       <c r="H3" t="n">
-        <v>1.502</v>
+        <v>1.5075</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5771</v>
+        <v>3.5734</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8873</v>
+        <v>3.8725</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2812</v>
+        <v>3.2692</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1919</v>
+        <v>1.2085</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8959</v>
+        <v>0.9043</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3006</v>
+        <v>0.0117</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2994</v>
+        <v>0.4899</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6001</v>
+        <v>-0.4782</v>
       </c>
       <c r="V3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4581</v>
+        <v>5.1721</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4829</v>
+        <v>2.6596</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9751</v>
+        <v>2.5125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9722</v>
+        <v>2.4124</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5626</v>
+        <v>0.928</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4096</v>
+        <v>1.4844</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4916</v>
+        <v>2.0815</v>
       </c>
       <c r="K4" t="n">
-        <v>1.967</v>
+        <v>0.9578</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5246</v>
+        <v>1.1237</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4806</v>
+        <v>0.331</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5956</v>
+        <v>-0.0298</v>
       </c>
       <c r="O4" t="n">
-        <v>0.885</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4178</v>
+        <v>1.4426</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1916</v>
+        <v>0.8545</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2262</v>
+        <v>0.5881</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7542</v>
+        <v>5.0417</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3356</v>
+        <v>3.2853</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4186</v>
+        <v>1.7564</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4342</v>
+        <v>4.9698</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9337</v>
+        <v>2.5674</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5006</v>
+        <v>2.4024</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1291</v>
+        <v>3.4624</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9831</v>
+        <v>1.951</v>
       </c>
       <c r="L5" t="n">
-        <v>1.146</v>
+        <v>1.5114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3052</v>
+        <v>1.5074</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0494</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3546</v>
+        <v>0.8911</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0005</v>
+        <v>1.0036</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4748</v>
+        <v>1.0309</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5256</v>
+        <v>-0.0273</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4752</v>
+        <v>4.6202</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3733</v>
+        <v>1.5534</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1019</v>
+        <v>3.0668</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2108</v>
+        <v>3.2234</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9767</v>
+        <v>1.9869</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2342</v>
+        <v>1.2365</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9812</v>
+        <v>1.9741</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2297</v>
+        <v>1.2493</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8165</v>
+        <v>0.832</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6539</v>
+        <v>0.7806</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5263</v>
+        <v>0.7175</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1276</v>
+        <v>0.0631</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5843</v>
+        <v>2.2063</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6947</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.279</v>
+        <v>2.8842</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0306</v>
+        <v>2.162</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2785</v>
+        <v>0.3643</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2479</v>
+        <v>1.7977</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.375</v>
+        <v>0.4954</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1456</v>
+        <v>-0.9415</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2293</v>
+        <v>1.4369</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4055</v>
+        <v>1.6666</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4241</v>
+        <v>1.3058</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0186</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.395</v>
+        <v>-0.6385</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2782</v>
+        <v>-0.0351</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6732</v>
+        <v>-0.6034</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4216</v>
+        <v>2.1261</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3118</v>
+        <v>0.0135</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7334</v>
+        <v>2.1126</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1608</v>
+        <v>0.0282</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3563</v>
+        <v>0.2786</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8045</v>
+        <v>-0.2504</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5179</v>
+        <v>-0.3906</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.1519</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4499</v>
+        <v>-0.2388</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6428</v>
+        <v>0.4189</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2883</v>
+        <v>0.4305</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3546</v>
+        <v>-0.0116</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4197</v>
+        <v>0.9386</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6956</v>
+        <v>0.4528</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7241</v>
+        <v>0.4857</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2032</v>
+        <v>1.3858</v>
       </c>
       <c r="E9" t="n">
-        <v>0.061</v>
+        <v>0.1704</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1422</v>
+        <v>1.2154</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2389</v>
+        <v>-0.2429</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.023</v>
+        <v>-0.0284</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5736</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0097</v>
+        <v>0.1718</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0514</v>
+        <v>0.0673</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8599</v>
+        <v>1.0309</v>
       </c>
       <c r="E10" t="n">
-        <v>1.655</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7951</v>
+        <v>1.8115</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6699000000000001</v>
+        <v>2.6905</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0446</v>
+        <v>0.7785</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7144</v>
+        <v>1.912</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1757</v>
+        <v>2.8176</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4369</v>
+        <v>1.2098</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2612</v>
+        <v>1.6077</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8455</v>
+        <v>-0.1271</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3923</v>
+        <v>-0.4314</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4532</v>
+        <v>0.3043</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-4.7803</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6022</v>
+        <v>1.9825</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8721</v>
+        <v>1.182</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7301</v>
+        <v>0.8005</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.655</v>
+        <v>-0.4926</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2265</v>
+        <v>0.7107</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8815</v>
+        <v>-1.2034</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7077</v>
+        <v>0.6688</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7806999999999999</v>
+        <v>-0.0541</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9271</v>
+        <v>0.7228</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8535</v>
+        <v>-0.195</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2224</v>
+        <v>-0.4556</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6311</v>
+        <v>0.2607</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1458</v>
+        <v>0.8638</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4417</v>
+        <v>0.4016</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2959</v>
+        <v>0.4622</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7635</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5766</v>
+        <v>1.2451</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6835</v>
+        <v>0.9544</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8931</v>
+        <v>0.2908</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2212</v>
+        <v>-1.3703</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6039</v>
+        <v>-1.0934</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6173</v>
+        <v>-0.2769</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2294</v>
+        <v>-0.2262</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3276</v>
+        <v>0.3247</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0323</v>
+        <v>-1.0479</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8028</v>
+        <v>0.8217</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1936</v>
+        <v>0.0349</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0162</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8227</v>
+        <v>-0.513</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7099</v>
+        <v>-2.6788</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0599</v>
+        <v>-2.068</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6499</v>
+        <v>-0.6108</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2952</v>
+        <v>-1.2943</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.293</v>
+        <v>-0.2902</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5736</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>0.039</v>
+        <v>0.0708</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.4348</v>
+        <v>30.47319999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>13.0908</v>
+        <v>13.8461</v>
       </c>
       <c r="F14" t="n">
-        <v>16.344</v>
+        <v>16.6269</v>
       </c>
       <c r="G14" t="n">
-        <v>22.456</v>
+        <v>22.4285</v>
       </c>
       <c r="H14" t="n">
-        <v>8.022500000000001</v>
+        <v>8.040799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>14.4336</v>
+        <v>14.3876</v>
       </c>
       <c r="J14" t="n">
-        <v>14.9706</v>
+        <v>14.7313</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7898</v>
+        <v>3.6686</v>
       </c>
       <c r="L14" t="n">
-        <v>11.1809</v>
+        <v>11.0627</v>
       </c>
       <c r="M14" t="n">
-        <v>7.4853</v>
+        <v>7.697500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2329</v>
+        <v>4.3723</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2525</v>
+        <v>3.325400000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.2682</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0126</v>
+        <v>-17.0726</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S14" t="n">
-        <v>7.3191</v>
+        <v>8.386300000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>6.230299999999999</v>
+        <v>7.314000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0885</v>
+        <v>1.0725</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9281</v>
+        <v>1.9349</v>
       </c>
       <c r="W14" t="n">
-        <v>8.902100000000001</v>
+        <v>8.873600000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.974</v>
+        <v>-6.9387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0986</v>
+        <v>0.2899</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1507</v>
+        <v>1.3228</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0522</v>
+        <v>-1.0329</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6145</v>
+        <v>0.3336</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1774</v>
+        <v>1.3878</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4371</v>
+        <v>-1.0542</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1395</v>
+        <v>2.2528</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0275</v>
+        <v>2.1784</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.754</v>
+        <v>-1.9193</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.205</v>
+        <v>-0.7906</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.549</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6716</v>
+        <v>-0.4275</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0113</v>
+        <v>-0.2652</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3396</v>
+        <v>-0.1623</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5018</v>
+        <v>-0.092</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5947</v>
+        <v>0.8497</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0929</v>
+        <v>-0.9417</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3349</v>
+        <v>-0.611</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3984</v>
+        <v>-0.1808</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0635</v>
+        <v>-0.4302</v>
       </c>
       <c r="J16" t="n">
-        <v>2.277</v>
+        <v>0.1322</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2023</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.942</v>
+        <v>-0.7432</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.2012</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1381</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2226</v>
+        <v>0.4703</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0302</v>
+        <v>0.7175</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1924</v>
+        <v>-0.2473</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4822</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,37 +1735,37 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8999</v>
+        <v>-0.8697</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7317</v>
+        <v>-0.7352</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1682</v>
+        <v>-0.1345</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9208</v>
+        <v>-0.922</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7317</v>
+        <v>-0.7352</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3375</v>
+        <v>-1.0877</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8744</v>
+        <v>-0.7694</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4631</v>
+        <v>-0.3183</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4754</v>
+        <v>-1.4709</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.404</v>
+        <v>-0.4076</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0715</v>
+        <v>-1.0632</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0579</v>
+        <v>-0.0699</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4176</v>
+        <v>-1.4009</v>
       </c>
       <c r="N18" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3157</v>
+        <v>-0.0721</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3176</v>
+        <v>0.4387</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6333</v>
+        <v>-0.5108</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4198</v>
+        <v>-1.46</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3229</v>
+        <v>0.3459</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9031</v>
+        <v>-1.8059</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6727</v>
+        <v>-0.2949</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1343</v>
+        <v>-1.1437</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5384</v>
+        <v>0.8488</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0353</v>
+        <v>0.4624</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3392</v>
+        <v>-0.669</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3039</v>
+        <v>1.1313</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.708</v>
+        <v>-0.7573</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4735</v>
+        <v>-0.4747</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>-0.2826</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2519</v>
+        <v>-0.4901</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>-0.1165</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2036</v>
+        <v>-0.3736</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>-2.7237</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5723</v>
+        <v>-1.6059</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3656</v>
+        <v>-2.4727</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9379</v>
+        <v>0.8668</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.299</v>
+        <v>-0.6688</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1545</v>
+        <v>-0.1295</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8556</v>
+        <v>-0.5393</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4836</v>
+        <v>0.0175</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6651</v>
+        <v>0.3308</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1487</v>
+        <v>-0.3132</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7825</v>
+        <v>-0.6863</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4894</v>
+        <v>-0.4603</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2931</v>
+        <v>-0.226</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0415</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5831</v>
+        <v>-0.4332</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1179</v>
+        <v>-0.1652</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4652</v>
+        <v>-0.268</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4436</v>
+        <v>-2.1063</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1849</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2586</v>
+        <v>-1.1441</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6798</v>
+        <v>-1.665</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3898</v>
+        <v>-0.3797</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2901</v>
+        <v>-1.2853</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1</v>
+        <v>-0.1049</v>
       </c>
       <c r="K21" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5798</v>
+        <v>-1.5601</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6296</v>
+        <v>-1.3032</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0434</v>
+        <v>-0.8087</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5861</v>
+        <v>-0.4945</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9988</v>
+        <v>-2.4479</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2455</v>
+        <v>-1.1705</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7533</v>
+        <v>-1.2775</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0721</v>
+        <v>-3.0785</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6563</v>
+        <v>-2.6675</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4158</v>
+        <v>-0.4109</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4419</v>
+        <v>-1.4779</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1828</v>
+        <v>-2.2073</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7409</v>
+        <v>0.7294</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6302</v>
+        <v>-1.6006</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3803</v>
+        <v>-0.8247</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3085</v>
+        <v>-0.1886</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0719</v>
+        <v>-0.6361</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2281</v>
+        <v>-3.0629</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.32</v>
+        <v>-2.9851</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0919</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2474</v>
+        <v>-1.2426</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6984</v>
+        <v>-0.7007</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2981</v>
+        <v>-0.2838</v>
       </c>
       <c r="N23" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7558</v>
+        <v>-0.5911</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1298</v>
+        <v>-0.3191</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3029</v>
+        <v>-3.1944</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1561</v>
+        <v>-2.5193</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1468</v>
+        <v>-0.6751</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9191</v>
+        <v>-2.8957</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2643</v>
+        <v>-0.2506</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6548</v>
+        <v>-2.6451</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.273</v>
+        <v>-1.2807</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2251</v>
+        <v>0.2241</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6461</v>
+        <v>-1.615</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8375</v>
+        <v>-0.7539</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2511</v>
+        <v>-0.1004</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0885</v>
+        <v>-0.6535</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5826</v>
+        <v>-5.9514</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9806</v>
+        <v>-2.662</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.602</v>
+        <v>-3.2894</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7769</v>
+        <v>-3.7818</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7964</v>
+        <v>-1.8006</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9805</v>
+        <v>-1.9812</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4289</v>
+        <v>-2.4506</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5279</v>
+        <v>-1.5416</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.348</v>
+        <v>-1.3312</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2594</v>
+        <v>-0.6249</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7906</v>
+        <v>-0.5108</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="26">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.2498</v>
+        <v>-6.26</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6389</v>
+        <v>-4.869</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6109</v>
+        <v>-1.391</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.1132</v>
+        <v>-6.131</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5739</v>
+        <v>-1.5984</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.5393</v>
+        <v>-4.5326</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.438</v>
+        <v>-3.4843</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1163</v>
+        <v>-1.1526</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.6752</v>
+        <v>-2.6467</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7756</v>
+        <v>-0.7632</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0253</v>
+        <v>-0.1979</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7504</v>
+        <v>-0.5653</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-29.4349</v>
+        <v>-27.84829999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-16.344</v>
+        <v>-16.627</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.0909</v>
+        <v>-11.2214</v>
       </c>
       <c r="G27" t="n">
-        <v>-22.456</v>
+        <v>-22.4286</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.022600000000001</v>
+        <v>-8.040900000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-14.4334</v>
+        <v>-14.3875</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.485300000000001</v>
+        <v>-7.6974</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.2329</v>
+        <v>-4.372300000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.2525</v>
+        <v>-3.325</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.9706</v>
+        <v>-14.7312</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.7896</v>
+        <v>-3.6686</v>
       </c>
       <c r="O27" t="n">
-        <v>-11.1808</v>
+        <v>-11.0625</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2684</v>
+        <v>2.276400000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.319</v>
+        <v>-5.7613</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.0886</v>
+        <v>-1.0724</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.2305</v>
+        <v>-4.688999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.9281</v>
+        <v>-1.9348</v>
       </c>
       <c r="W27" t="n">
-        <v>6.974099999999999</v>
+        <v>6.9387</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.902100000000001</v>
+        <v>-8.8736</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104466_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104466_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.9387</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104466_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-8.8736</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
